--- a/XII B INFORMATION.xlsx
+++ b/XII B INFORMATION.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="728">
   <si>
     <t>S.NO.</t>
   </si>
@@ -9960,24 +9960,17 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="65" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="65" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AA65" s="78"/>
       <c r="AB65" s="78"/>
       <c r="AC65" s="79"/>
-      <c r="AE65" s="1">
-        <f>SUM(AE2:AE64)</f>
-        <v>219640</v>
-      </c>
-    </row>
-    <row r="66" spans="11:31" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AA66" s="80"/>
       <c r="AB66" s="80"/>
       <c r="AC66" s="80"/>
     </row>
-    <row r="67" spans="11:31" x14ac:dyDescent="0.35">
-      <c r="K67">
-        <v>119745</v>
-      </c>
+    <row r="67" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q67" s="45"/>
       <c r="R67" s="45"/>
       <c r="S67" s="45"/>
@@ -9992,7 +9985,7 @@
       <c r="AB67" s="80"/>
       <c r="AC67" s="80"/>
     </row>
-    <row r="68" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="68" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q68" s="45"/>
       <c r="R68" s="45"/>
       <c r="S68" s="45"/>
@@ -10007,7 +10000,7 @@
       <c r="AB68" s="80"/>
       <c r="AC68" s="80"/>
     </row>
-    <row r="69" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="69" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q69" s="45"/>
       <c r="R69" s="45"/>
       <c r="S69" s="45"/>
@@ -10022,7 +10015,7 @@
       <c r="AB69" s="80"/>
       <c r="AC69" s="80"/>
     </row>
-    <row r="70" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="70" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q70" s="45"/>
       <c r="R70" s="45"/>
       <c r="S70" s="45"/>
@@ -10037,7 +10030,7 @@
       <c r="AB70" s="80"/>
       <c r="AC70" s="80"/>
     </row>
-    <row r="71" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="71" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q71" s="45"/>
       <c r="R71" s="45"/>
       <c r="S71" s="45"/>
@@ -10052,7 +10045,7 @@
       <c r="AB71" s="80"/>
       <c r="AC71" s="80"/>
     </row>
-    <row r="72" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="72" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q72" s="45"/>
       <c r="R72" s="45"/>
       <c r="S72" s="45"/>
@@ -10067,7 +10060,7 @@
       <c r="AB72" s="78"/>
       <c r="AC72" s="78"/>
     </row>
-    <row r="73" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="73" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q73" s="45"/>
       <c r="R73" s="45"/>
       <c r="S73" s="45"/>
@@ -10082,7 +10075,7 @@
       <c r="AB73" s="80"/>
       <c r="AC73" s="45"/>
     </row>
-    <row r="74" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="74" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q74" s="45"/>
       <c r="R74" s="45"/>
       <c r="S74" s="45"/>
@@ -10097,7 +10090,7 @@
       <c r="AB74" s="80"/>
       <c r="AC74" s="80"/>
     </row>
-    <row r="75" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="75" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q75" s="45"/>
       <c r="R75" s="45"/>
       <c r="S75" s="45"/>
@@ -10108,17 +10101,11 @@
       <c r="X75" s="45"/>
       <c r="Y75" s="45"/>
       <c r="Z75" s="45"/>
-      <c r="AA75" s="81" t="s">
-        <v>608</v>
-      </c>
-      <c r="AB75" s="81" t="s">
-        <v>378</v>
-      </c>
-      <c r="AC75" s="81" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="11:31" x14ac:dyDescent="0.35">
+      <c r="AA75" s="81"/>
+      <c r="AB75" s="81"/>
+      <c r="AC75" s="81"/>
+    </row>
+    <row r="76" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q76" s="45"/>
       <c r="R76" s="45"/>
       <c r="S76" s="45"/>
@@ -10129,17 +10116,11 @@
       <c r="X76" s="45"/>
       <c r="Y76" s="45"/>
       <c r="Z76" s="45"/>
-      <c r="AA76" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB76" s="44">
-        <v>2</v>
-      </c>
-      <c r="AC76" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="11:31" x14ac:dyDescent="0.35">
+      <c r="AA76" s="81"/>
+      <c r="AB76" s="44"/>
+      <c r="AC76" s="44"/>
+    </row>
+    <row r="77" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q77" s="45"/>
       <c r="R77" s="45"/>
       <c r="S77" s="45"/>
@@ -10150,17 +10131,11 @@
       <c r="X77" s="45"/>
       <c r="Y77" s="45"/>
       <c r="Z77" s="45"/>
-      <c r="AA77" s="81" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB77" s="44">
-        <v>1</v>
-      </c>
-      <c r="AC77" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="11:31" x14ac:dyDescent="0.35">
+      <c r="AA77" s="81"/>
+      <c r="AB77" s="44"/>
+      <c r="AC77" s="44"/>
+    </row>
+    <row r="78" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q78" s="45"/>
       <c r="R78" s="45"/>
       <c r="S78" s="45"/>
@@ -10171,15 +10146,11 @@
       <c r="X78" s="45"/>
       <c r="Y78" s="45"/>
       <c r="Z78" s="45"/>
-      <c r="AA78" s="81" t="s">
-        <v>49</v>
-      </c>
+      <c r="AA78" s="81"/>
       <c r="AB78" s="44"/>
-      <c r="AC78" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="11:31" x14ac:dyDescent="0.35">
+      <c r="AC78" s="44"/>
+    </row>
+    <row r="79" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q79" s="45"/>
       <c r="R79" s="45"/>
       <c r="S79" s="45"/>
@@ -10196,7 +10167,7 @@
       <c r="AB79" s="44"/>
       <c r="AC79" s="44"/>
     </row>
-    <row r="80" spans="11:31" x14ac:dyDescent="0.35">
+    <row r="80" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q80" s="45"/>
       <c r="R80" s="45"/>
       <c r="S80" s="45"/>
@@ -10212,11 +10183,11 @@
       </c>
       <c r="AB80" s="44">
         <f>SUBTOTAL(9,AB76:AB79)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC80" s="44">
         <f>SUBTOTAL(9,AC76:AC79)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="17:29" x14ac:dyDescent="0.35">

--- a/XII B INFORMATION.xlsx
+++ b/XII B INFORMATION.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="727">
   <si>
     <t>S.NO.</t>
   </si>
@@ -1928,9 +1928,6 @@
   </si>
   <si>
     <t>031028</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>DEPT</t>
@@ -2984,7 +2981,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -3200,9 +3197,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3657,391 +3651,391 @@
     <col min="9" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="99" customFormat="1" ht="21" x14ac:dyDescent="0.5">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:8" s="98" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="A1" s="124" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+    </row>
+    <row r="2" spans="1:8" s="97" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="107" t="s">
+        <v>636</v>
+      </c>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="109"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="99" t="s">
+        <v>633</v>
+      </c>
+      <c r="C3" s="99" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="99" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="99" t="s">
+        <v>601</v>
+      </c>
+      <c r="G3" s="99" t="s">
+        <v>602</v>
+      </c>
+      <c r="H3" s="105" t="s">
         <v>635</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-    </row>
-    <row r="2" spans="1:8" s="98" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="108" t="s">
-        <v>637</v>
-      </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="110"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="100" t="s">
-        <v>634</v>
-      </c>
-      <c r="C3" s="100" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="91">
         <v>1</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="B4" s="91">
+        <v>5</v>
+      </c>
+      <c r="C4" s="92">
+        <v>37239</v>
+      </c>
+      <c r="D4" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="95" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="100" t="s">
+        <v>605</v>
+      </c>
+      <c r="G4" s="95" t="s">
+        <v>606</v>
+      </c>
+      <c r="H4" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="91">
+        <v>2</v>
+      </c>
+      <c r="B5" s="91">
+        <v>10</v>
+      </c>
+      <c r="C5" s="92">
+        <v>39076</v>
+      </c>
+      <c r="D5" s="94" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" s="95" t="s">
+        <v>353</v>
+      </c>
+      <c r="F5" s="100" t="s">
+        <v>609</v>
+      </c>
+      <c r="G5" s="95" t="s">
+        <v>610</v>
+      </c>
+      <c r="H5" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="91">
+        <v>3</v>
+      </c>
+      <c r="B6" s="91">
+        <v>20</v>
+      </c>
+      <c r="C6" s="92">
+        <v>37253</v>
+      </c>
+      <c r="D6" s="94" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="95" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="100" t="s">
+        <v>611</v>
+      </c>
+      <c r="G6" s="95" t="s">
+        <v>612</v>
+      </c>
+      <c r="H6" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="91">
+        <v>4</v>
+      </c>
+      <c r="B7" s="91">
+        <v>27</v>
+      </c>
+      <c r="C7" s="92">
+        <v>39007</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" s="101" t="s">
+        <v>613</v>
+      </c>
+      <c r="G7" s="96" t="s">
+        <v>610</v>
+      </c>
+      <c r="H7" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="91">
+        <v>5</v>
+      </c>
+      <c r="B8" s="91">
+        <v>30</v>
+      </c>
+      <c r="C8" s="92">
+        <v>37181</v>
+      </c>
+      <c r="D8" s="96" t="s">
+        <v>263</v>
+      </c>
+      <c r="E8" s="96" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="102" t="s">
+        <v>614</v>
+      </c>
+      <c r="G8" s="96" t="s">
+        <v>610</v>
+      </c>
+      <c r="H8" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="91">
+        <v>6</v>
+      </c>
+      <c r="B9" s="91">
+        <v>39</v>
+      </c>
+      <c r="C9" s="93" t="s">
+        <v>573</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>574</v>
+      </c>
+      <c r="E9" s="95" t="s">
+        <v>576</v>
+      </c>
+      <c r="F9" s="100" t="s">
+        <v>615</v>
+      </c>
+      <c r="G9" s="95" t="s">
+        <v>616</v>
+      </c>
+      <c r="H9" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="91">
+        <v>7</v>
+      </c>
+      <c r="B10" s="91">
+        <v>40</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>381</v>
+      </c>
+      <c r="D10" s="94" t="s">
+        <v>382</v>
+      </c>
+      <c r="E10" s="95" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10" s="103" t="s">
+        <v>617</v>
+      </c>
+      <c r="G10" s="95" t="s">
+        <v>616</v>
+      </c>
+      <c r="H10" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="91">
+        <v>8</v>
+      </c>
+      <c r="B11" s="91">
+        <v>41</v>
+      </c>
+      <c r="C11" s="92">
+        <v>38990</v>
+      </c>
+      <c r="D11" s="94" t="s">
+        <v>391</v>
+      </c>
+      <c r="E11" s="95" t="s">
+        <v>393</v>
+      </c>
+      <c r="F11" s="100" t="s">
+        <v>618</v>
+      </c>
+      <c r="G11" s="95" t="s">
+        <v>619</v>
+      </c>
+      <c r="H11" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="91">
         <v>9</v>
       </c>
-      <c r="E3" s="100" t="s">
+      <c r="B12" s="91">
+        <v>48</v>
+      </c>
+      <c r="C12" s="92">
+        <v>38999</v>
+      </c>
+      <c r="D12" s="94" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="F12" s="100" t="s">
+        <v>620</v>
+      </c>
+      <c r="G12" s="95" t="s">
+        <v>621</v>
+      </c>
+      <c r="H12" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="91">
+        <v>10</v>
+      </c>
+      <c r="B13" s="91">
+        <v>50</v>
+      </c>
+      <c r="C13" s="92">
+        <v>37069</v>
+      </c>
+      <c r="D13" s="94" t="s">
+        <v>599</v>
+      </c>
+      <c r="E13" s="95" t="s">
+        <v>455</v>
+      </c>
+      <c r="F13" s="104" t="s">
+        <v>622</v>
+      </c>
+      <c r="G13" s="95" t="s">
+        <v>623</v>
+      </c>
+      <c r="H13" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="91">
         <v>11</v>
       </c>
-      <c r="F3" s="100" t="s">
-        <v>601</v>
-      </c>
-      <c r="G3" s="100" t="s">
-        <v>602</v>
-      </c>
-      <c r="H3" s="106" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="92">
-        <v>1</v>
-      </c>
-      <c r="B4" s="92">
-        <v>5</v>
-      </c>
-      <c r="C4" s="93">
-        <v>37239</v>
-      </c>
-      <c r="D4" s="95" t="s">
+      <c r="B14" s="91">
+        <v>51</v>
+      </c>
+      <c r="C14" s="92">
+        <v>37068</v>
+      </c>
+      <c r="D14" s="94" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14" s="95" t="s">
+        <v>483</v>
+      </c>
+      <c r="F14" s="100" t="s">
+        <v>624</v>
+      </c>
+      <c r="G14" s="95" t="s">
+        <v>610</v>
+      </c>
+      <c r="H14" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="91">
+        <v>12</v>
+      </c>
+      <c r="B15" s="91">
         <v>55</v>
       </c>
-      <c r="E4" s="96" t="s">
+      <c r="C15" s="92">
+        <v>37143</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>506</v>
+      </c>
+      <c r="E15" s="95" t="s">
+        <v>508</v>
+      </c>
+      <c r="F15" s="100" t="s">
+        <v>625</v>
+      </c>
+      <c r="G15" s="95" t="s">
+        <v>616</v>
+      </c>
+      <c r="H15" s="106">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="91">
+        <v>13</v>
+      </c>
+      <c r="B16" s="91">
         <v>57</v>
       </c>
-      <c r="F4" s="101" t="s">
-        <v>605</v>
-      </c>
-      <c r="G4" s="96" t="s">
-        <v>606</v>
-      </c>
-      <c r="H4" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92">
-        <v>2</v>
-      </c>
-      <c r="B5" s="92">
-        <v>10</v>
-      </c>
-      <c r="C5" s="93">
-        <v>39076</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>351</v>
-      </c>
-      <c r="E5" s="96" t="s">
-        <v>353</v>
-      </c>
-      <c r="F5" s="101" t="s">
-        <v>609</v>
-      </c>
-      <c r="G5" s="96" t="s">
-        <v>610</v>
-      </c>
-      <c r="H5" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92">
-        <v>3</v>
-      </c>
-      <c r="B6" s="92">
-        <v>20</v>
-      </c>
-      <c r="C6" s="93">
-        <v>37253</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="101" t="s">
-        <v>611</v>
-      </c>
-      <c r="G6" s="96" t="s">
-        <v>612</v>
-      </c>
-      <c r="H6" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92">
-        <v>4</v>
-      </c>
-      <c r="B7" s="92">
-        <v>27</v>
-      </c>
-      <c r="C7" s="93">
-        <v>39007</v>
-      </c>
-      <c r="D7" s="97" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="97" t="s">
-        <v>241</v>
-      </c>
-      <c r="F7" s="102" t="s">
-        <v>613</v>
-      </c>
-      <c r="G7" s="97" t="s">
-        <v>610</v>
-      </c>
-      <c r="H7" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92">
-        <v>5</v>
-      </c>
-      <c r="B8" s="92">
-        <v>30</v>
-      </c>
-      <c r="C8" s="93">
-        <v>37181</v>
-      </c>
-      <c r="D8" s="97" t="s">
-        <v>263</v>
-      </c>
-      <c r="E8" s="97" t="s">
-        <v>265</v>
-      </c>
-      <c r="F8" s="103" t="s">
-        <v>614</v>
-      </c>
-      <c r="G8" s="97" t="s">
-        <v>610</v>
-      </c>
-      <c r="H8" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92">
-        <v>6</v>
-      </c>
-      <c r="B9" s="92">
-        <v>39</v>
-      </c>
-      <c r="C9" s="94" t="s">
-        <v>573</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>574</v>
-      </c>
-      <c r="E9" s="96" t="s">
-        <v>576</v>
-      </c>
-      <c r="F9" s="101" t="s">
-        <v>615</v>
-      </c>
-      <c r="G9" s="96" t="s">
+      <c r="C16" s="93">
+        <v>37124</v>
+      </c>
+      <c r="D16" s="94" t="s">
+        <v>542</v>
+      </c>
+      <c r="E16" s="95" t="s">
+        <v>544</v>
+      </c>
+      <c r="F16" s="100" t="s">
+        <v>626</v>
+      </c>
+      <c r="G16" s="95" t="s">
         <v>616</v>
       </c>
-      <c r="H9" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="92">
-        <v>7</v>
-      </c>
-      <c r="B10" s="92">
-        <v>40</v>
-      </c>
-      <c r="C10" s="93" t="s">
-        <v>381</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>382</v>
-      </c>
-      <c r="E10" s="96" t="s">
-        <v>384</v>
-      </c>
-      <c r="F10" s="104" t="s">
-        <v>617</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>616</v>
-      </c>
-      <c r="H10" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="92">
-        <v>8</v>
-      </c>
-      <c r="B11" s="92">
-        <v>41</v>
-      </c>
-      <c r="C11" s="93">
-        <v>38990</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>391</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>393</v>
-      </c>
-      <c r="F11" s="101" t="s">
-        <v>618</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>619</v>
-      </c>
-      <c r="H11" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="92">
-        <v>9</v>
-      </c>
-      <c r="B12" s="92">
-        <v>48</v>
-      </c>
-      <c r="C12" s="93">
-        <v>38999</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>462</v>
-      </c>
-      <c r="E12" s="96" t="s">
-        <v>464</v>
-      </c>
-      <c r="F12" s="101" t="s">
-        <v>620</v>
-      </c>
-      <c r="G12" s="96" t="s">
-        <v>621</v>
-      </c>
-      <c r="H12" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="92">
-        <v>10</v>
-      </c>
-      <c r="B13" s="92">
-        <v>50</v>
-      </c>
-      <c r="C13" s="93">
-        <v>37069</v>
-      </c>
-      <c r="D13" s="95" t="s">
-        <v>599</v>
-      </c>
-      <c r="E13" s="96" t="s">
-        <v>455</v>
-      </c>
-      <c r="F13" s="105" t="s">
-        <v>622</v>
-      </c>
-      <c r="G13" s="96" t="s">
-        <v>623</v>
-      </c>
-      <c r="H13" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="92">
-        <v>11</v>
-      </c>
-      <c r="B14" s="92">
-        <v>51</v>
-      </c>
-      <c r="C14" s="93">
-        <v>37068</v>
-      </c>
-      <c r="D14" s="95" t="s">
-        <v>481</v>
-      </c>
-      <c r="E14" s="96" t="s">
-        <v>483</v>
-      </c>
-      <c r="F14" s="101" t="s">
-        <v>624</v>
-      </c>
-      <c r="G14" s="96" t="s">
-        <v>610</v>
-      </c>
-      <c r="H14" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="92">
-        <v>12</v>
-      </c>
-      <c r="B15" s="92">
-        <v>55</v>
-      </c>
-      <c r="C15" s="93">
-        <v>37143</v>
-      </c>
-      <c r="D15" s="95" t="s">
-        <v>506</v>
-      </c>
-      <c r="E15" s="96" t="s">
-        <v>508</v>
-      </c>
-      <c r="F15" s="101" t="s">
-        <v>625</v>
-      </c>
-      <c r="G15" s="96" t="s">
-        <v>616</v>
-      </c>
-      <c r="H15" s="107">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="92">
-        <v>13</v>
-      </c>
-      <c r="B16" s="92">
-        <v>57</v>
-      </c>
-      <c r="C16" s="94">
-        <v>37124</v>
-      </c>
-      <c r="D16" s="95" t="s">
-        <v>542</v>
-      </c>
-      <c r="E16" s="96" t="s">
-        <v>544</v>
-      </c>
-      <c r="F16" s="101" t="s">
-        <v>626</v>
-      </c>
-      <c r="G16" s="96" t="s">
-        <v>616</v>
-      </c>
-      <c r="H16" s="107">
+      <c r="H16" s="106">
         <v>4435</v>
       </c>
     </row>
@@ -4107,86 +4101,86 @@
     <col min="31" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="112" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+    <row r="1" spans="1:32" s="111" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="112" t="s">
         <v>595</v>
       </c>
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="112" t="s">
         <v>590</v>
       </c>
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="113" t="s">
+      <c r="F1" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="113" t="s">
+      <c r="H1" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="113" t="s">
+      <c r="J1" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="113" t="s">
+      <c r="K1" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="113" t="s">
+      <c r="L1" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="113" t="s">
+      <c r="M1" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="113" t="s">
+      <c r="N1" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="113" t="s">
+      <c r="O1" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="113" t="s">
+      <c r="P1" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="113" t="s">
+      <c r="Q1" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113" t="s">
+      <c r="R1" s="112"/>
+      <c r="S1" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="113" t="s">
+      <c r="T1" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113" t="s">
+      <c r="U1" s="112"/>
+      <c r="V1" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113" t="s">
+      <c r="W1" s="112"/>
+      <c r="X1" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="113" t="s">
+      <c r="Y1" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="113" t="s">
+      <c r="Z1" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="111" t="s">
+      <c r="AA1" s="110" t="s">
         <v>600</v>
       </c>
-      <c r="AB1" s="111" t="s">
+      <c r="AB1" s="110" t="s">
         <v>601</v>
       </c>
-      <c r="AC1" s="111" t="s">
+      <c r="AC1" s="110" t="s">
         <v>602</v>
       </c>
     </row>
@@ -4274,12 +4268,7 @@
       </c>
       <c r="AB2" s="57"/>
       <c r="AC2" s="57"/>
-      <c r="AE2" s="1">
-        <v>4465</v>
-      </c>
-      <c r="AF2" s="120">
-        <v>46148</v>
-      </c>
+      <c r="AF2" s="119"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
@@ -4365,15 +4354,7 @@
       </c>
       <c r="AB3" s="59"/>
       <c r="AC3" s="60"/>
-      <c r="AD3" s="1">
-        <v>9956848055</v>
-      </c>
-      <c r="AE3" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF3" s="120">
-        <v>46143</v>
-      </c>
+      <c r="AF3" s="119"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
@@ -4459,12 +4440,7 @@
       </c>
       <c r="AB4" s="59"/>
       <c r="AC4" s="60"/>
-      <c r="AE4" s="1">
-        <v>4445</v>
-      </c>
-      <c r="AF4" s="120">
-        <v>46144</v>
-      </c>
+      <c r="AF4" s="119"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -4550,12 +4526,7 @@
       </c>
       <c r="AB5" s="61"/>
       <c r="AC5" s="56"/>
-      <c r="AE5" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF5" s="120">
-        <v>46121</v>
-      </c>
+      <c r="AF5" s="119"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
@@ -4734,12 +4705,7 @@
       <c r="AC7" s="63" t="s">
         <v>607</v>
       </c>
-      <c r="AE7" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF7" s="120">
-        <v>46138</v>
-      </c>
+      <c r="AF7" s="119"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -4825,12 +4791,7 @@
       </c>
       <c r="AB8" s="65"/>
       <c r="AC8" s="64"/>
-      <c r="AE8" s="1">
-        <v>4455</v>
-      </c>
-      <c r="AF8" s="120">
-        <v>46146</v>
-      </c>
+      <c r="AF8" s="119"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -4916,12 +4877,7 @@
       </c>
       <c r="AB9" s="59"/>
       <c r="AC9" s="60"/>
-      <c r="AE9" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF9" s="120">
-        <v>46141</v>
-      </c>
+      <c r="AF9" s="119"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -4954,7 +4910,7 @@
       <c r="J10" s="6">
         <v>2008</v>
       </c>
-      <c r="K10" s="85" t="s">
+      <c r="K10" s="84" t="s">
         <v>87</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -5011,12 +4967,7 @@
       <c r="AC10" s="63" t="s">
         <v>607</v>
       </c>
-      <c r="AE10" s="1">
-        <v>4445</v>
-      </c>
-      <c r="AF10" s="120">
-        <v>46145</v>
-      </c>
+      <c r="AF10" s="119"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -5100,18 +5051,13 @@
       <c r="AA11" s="56" t="s">
         <v>604</v>
       </c>
-      <c r="AB11" s="90" t="s">
+      <c r="AB11" s="89" t="s">
         <v>609</v>
       </c>
       <c r="AC11" s="56" t="s">
         <v>610</v>
       </c>
-      <c r="AE11" s="1">
-        <v>4510</v>
-      </c>
-      <c r="AF11" s="120">
-        <v>46157</v>
-      </c>
+      <c r="AF11" s="119"/>
     </row>
     <row r="12" spans="1:32" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
@@ -5197,12 +5143,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AC12" s="57"/>
-      <c r="AE12" s="1">
-        <v>4505</v>
-      </c>
-      <c r="AF12" s="120">
-        <v>46156</v>
-      </c>
+      <c r="AF12" s="119"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
@@ -5235,7 +5176,7 @@
       <c r="J13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="86" t="s">
+      <c r="K13" s="85" t="s">
         <v>109</v>
       </c>
       <c r="L13" s="7" t="s">
@@ -5292,12 +5233,7 @@
       <c r="AC13" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE13" s="1">
-        <v>4510</v>
-      </c>
-      <c r="AF13" s="120">
-        <v>46157</v>
-      </c>
+      <c r="AF13" s="119"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
@@ -5383,12 +5319,7 @@
       </c>
       <c r="AB14" s="61"/>
       <c r="AC14" s="56"/>
-      <c r="AE14" s="1">
-        <v>4455</v>
-      </c>
-      <c r="AF14" s="120">
-        <v>46146</v>
-      </c>
+      <c r="AF14" s="119"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -5563,12 +5494,7 @@
       <c r="AC16" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE16" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF16" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF16" s="119"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
@@ -5654,12 +5580,7 @@
       </c>
       <c r="AB17" s="57"/>
       <c r="AC17" s="57"/>
-      <c r="AE17" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF17" s="120">
-        <v>46136</v>
-      </c>
+      <c r="AF17" s="119"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -5745,12 +5666,7 @@
       </c>
       <c r="AB18" s="65"/>
       <c r="AC18" s="64"/>
-      <c r="AE18" s="1">
-        <v>4445</v>
-      </c>
-      <c r="AF18" s="120">
-        <v>46144</v>
-      </c>
+      <c r="AF18" s="119"/>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
@@ -5836,12 +5752,7 @@
       </c>
       <c r="AB19" s="57"/>
       <c r="AC19" s="57"/>
-      <c r="AE19" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF19" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF19" s="119"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
@@ -5927,12 +5838,7 @@
       </c>
       <c r="AB20" s="61"/>
       <c r="AC20" s="63"/>
-      <c r="AE20" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF20" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF20" s="119"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
@@ -6016,7 +5922,7 @@
       <c r="AA21" s="56" t="s">
         <v>604</v>
       </c>
-      <c r="AB21" s="89" t="s">
+      <c r="AB21" s="88" t="s">
         <v>611</v>
       </c>
       <c r="AC21" s="56" t="s">
@@ -6111,12 +6017,7 @@
       <c r="AC22" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE22" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF22" s="120">
-        <v>46124</v>
-      </c>
+      <c r="AF22" s="119"/>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
@@ -6202,12 +6103,7 @@
       </c>
       <c r="AB23" s="59"/>
       <c r="AC23" s="60"/>
-      <c r="AE23" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF23" s="120">
-        <v>46128</v>
-      </c>
+      <c r="AF23" s="119"/>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
@@ -6240,7 +6136,7 @@
       <c r="J24" s="22">
         <v>2008</v>
       </c>
-      <c r="K24" s="85" t="s">
+      <c r="K24" s="84" t="s">
         <v>202</v>
       </c>
       <c r="L24" s="9" t="s">
@@ -6297,12 +6193,7 @@
       <c r="AC24" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE24" s="1">
-        <v>4780</v>
-      </c>
-      <c r="AF24" s="120">
-        <v>46209</v>
-      </c>
+      <c r="AF24" s="119"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
@@ -6388,12 +6279,7 @@
       </c>
       <c r="AB25" s="61"/>
       <c r="AC25" s="63"/>
-      <c r="AE25" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF25" s="120">
-        <v>46121</v>
-      </c>
+      <c r="AF25" s="119"/>
     </row>
     <row r="26" spans="1:32" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
@@ -6479,12 +6365,7 @@
       </c>
       <c r="AB26" s="61"/>
       <c r="AC26" s="63"/>
-      <c r="AE26" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF26" s="120">
-        <v>46139</v>
-      </c>
+      <c r="AF26" s="119"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
@@ -6570,12 +6451,7 @@
       </c>
       <c r="AB27" s="61"/>
       <c r="AC27" s="63"/>
-      <c r="AE27" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF27" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF27" s="119"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
@@ -6754,12 +6630,7 @@
       <c r="AC29" s="70" t="s">
         <v>607</v>
       </c>
-      <c r="AE29" s="1">
-        <v>4510</v>
-      </c>
-      <c r="AF29" s="120">
-        <v>46157</v>
-      </c>
+      <c r="AF29" s="119"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
@@ -6792,7 +6663,7 @@
       <c r="J30" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="87" t="s">
+      <c r="K30" s="86" t="s">
         <v>256</v>
       </c>
       <c r="L30" s="27" t="s">
@@ -6849,12 +6720,7 @@
       <c r="AC30" s="70" t="s">
         <v>607</v>
       </c>
-      <c r="AE30" s="1">
-        <v>4470</v>
-      </c>
-      <c r="AF30" s="120">
-        <v>46149</v>
-      </c>
+      <c r="AF30" s="119"/>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
@@ -6938,7 +6804,7 @@
       <c r="AA31" s="67" t="s">
         <v>604</v>
       </c>
-      <c r="AB31" s="88" t="s">
+      <c r="AB31" s="87" t="s">
         <v>614</v>
       </c>
       <c r="AC31" s="67" t="s">
@@ -7029,12 +6895,7 @@
       </c>
       <c r="AB32" s="71"/>
       <c r="AC32" s="63"/>
-      <c r="AE32" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF32" s="120">
-        <v>46131</v>
-      </c>
+      <c r="AF32" s="119"/>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
@@ -7124,12 +6985,7 @@
       <c r="AC33" s="63" t="s">
         <v>607</v>
       </c>
-      <c r="AE33" s="1">
-        <v>4955</v>
-      </c>
-      <c r="AF33" s="120">
-        <v>46246</v>
-      </c>
+      <c r="AF33" s="119"/>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
@@ -7219,12 +7075,7 @@
       <c r="AC34" s="70" t="s">
         <v>607</v>
       </c>
-      <c r="AE34" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF34" s="120">
-        <v>46117</v>
-      </c>
+      <c r="AF34" s="119"/>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
@@ -7314,12 +7165,7 @@
       <c r="AC35" s="70" t="s">
         <v>607</v>
       </c>
-      <c r="AE35" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF35" s="120">
-        <v>46130</v>
-      </c>
+      <c r="AF35" s="119"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
@@ -7405,12 +7251,7 @@
       </c>
       <c r="AB36" s="72"/>
       <c r="AC36" s="60"/>
-      <c r="AE36" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF36" s="120">
-        <v>46143</v>
-      </c>
+      <c r="AF36" s="119"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
@@ -7496,12 +7337,7 @@
       </c>
       <c r="AB37" s="59"/>
       <c r="AC37" s="60"/>
-      <c r="AE37" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF37" s="120">
-        <v>46135</v>
-      </c>
+      <c r="AF37" s="119"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
@@ -7587,12 +7423,7 @@
       </c>
       <c r="AB38" s="74"/>
       <c r="AC38" s="57"/>
-      <c r="AE38" s="1">
-        <v>4770</v>
-      </c>
-      <c r="AF38" s="120">
-        <v>46209</v>
-      </c>
+      <c r="AF38" s="119"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
@@ -7682,12 +7513,7 @@
       <c r="AC39" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE39" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF39" s="120">
-        <v>46139</v>
-      </c>
+      <c r="AF39" s="119"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
@@ -7771,7 +7597,7 @@
       <c r="AA40" s="56" t="s">
         <v>604</v>
       </c>
-      <c r="AB40" s="91" t="s">
+      <c r="AB40" s="90" t="s">
         <v>615</v>
       </c>
       <c r="AC40" s="56" t="s">
@@ -8044,12 +7870,7 @@
       <c r="AC43" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE43" s="1">
-        <v>4520</v>
-      </c>
-      <c r="AF43" s="120">
-        <v>46155</v>
-      </c>
+      <c r="AF43" s="119"/>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
@@ -8082,7 +7903,7 @@
       <c r="J44" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K44" s="86" t="s">
+      <c r="K44" s="85" t="s">
         <v>598</v>
       </c>
       <c r="L44" s="7" t="s">
@@ -8135,12 +7956,7 @@
       </c>
       <c r="AB44" s="57"/>
       <c r="AC44" s="65"/>
-      <c r="AE44" s="1">
-        <v>4450</v>
-      </c>
-      <c r="AF44" s="120">
-        <v>46145</v>
-      </c>
+      <c r="AF44" s="119"/>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
@@ -8173,7 +7989,7 @@
       <c r="J45" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K45" s="85" t="s">
+      <c r="K45" s="84" t="s">
         <v>407</v>
       </c>
       <c r="L45" s="9" t="s">
@@ -8226,12 +8042,7 @@
       </c>
       <c r="AB45" s="66"/>
       <c r="AC45" s="56"/>
-      <c r="AE45" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF45" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF45" s="119"/>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
@@ -8317,12 +8128,7 @@
       </c>
       <c r="AB46" s="56"/>
       <c r="AC46" s="57"/>
-      <c r="AE46" s="1">
-        <v>4530</v>
-      </c>
-      <c r="AF46" s="120">
-        <v>46161</v>
-      </c>
+      <c r="AF46" s="119"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
@@ -8412,12 +8218,7 @@
       <c r="AC47" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE47" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF47" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF47" s="119"/>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
@@ -8450,7 +8251,7 @@
       <c r="J48" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="K48" s="86" t="s">
+      <c r="K48" s="85" t="s">
         <v>432</v>
       </c>
       <c r="L48" s="7" t="s">
@@ -8503,12 +8304,7 @@
       </c>
       <c r="AB48" s="56"/>
       <c r="AC48" s="57"/>
-      <c r="AE48" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF48" s="120">
-        <v>46116</v>
-      </c>
+      <c r="AF48" s="119"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
@@ -8592,7 +8388,7 @@
       <c r="AA49" s="56" t="s">
         <v>604</v>
       </c>
-      <c r="AB49" s="89" t="s">
+      <c r="AB49" s="88" t="s">
         <v>620</v>
       </c>
       <c r="AC49" s="56" t="s">
@@ -8687,12 +8483,7 @@
       <c r="AC50" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE50" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF50" s="120">
-        <v>46136</v>
-      </c>
+      <c r="AF50" s="119"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
@@ -8956,12 +8747,7 @@
       </c>
       <c r="AB53" s="66"/>
       <c r="AC53" s="56"/>
-      <c r="AE53" s="1">
-        <v>4845</v>
-      </c>
-      <c r="AF53" s="120">
-        <v>46224</v>
-      </c>
+      <c r="AF53" s="119"/>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
@@ -9132,13 +8918,8 @@
       </c>
       <c r="AB55" s="66"/>
       <c r="AC55" s="56"/>
-      <c r="AE55" s="1">
-        <v>4490</v>
-      </c>
-      <c r="AF55" s="120">
-        <v>46151</v>
-      </c>
-      <c r="AG55" s="120"/>
+      <c r="AF55" s="119"/>
+      <c r="AG55" s="119"/>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
@@ -9313,13 +9094,8 @@
       </c>
       <c r="AB57" s="66"/>
       <c r="AC57" s="56"/>
-      <c r="AE57" s="1">
-        <v>4470</v>
-      </c>
-      <c r="AF57" s="120">
-        <v>46149</v>
-      </c>
-      <c r="AG57" s="120"/>
+      <c r="AF57" s="119"/>
+      <c r="AG57" s="119"/>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
@@ -9441,7 +9217,7 @@
       <c r="J59" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K59" s="86" t="s">
+      <c r="K59" s="85" t="s">
         <v>521</v>
       </c>
       <c r="L59" s="9" t="s">
@@ -9494,12 +9270,7 @@
       </c>
       <c r="AB59" s="62"/>
       <c r="AC59" s="56"/>
-      <c r="AE59" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF59" s="120">
-        <v>46136</v>
-      </c>
+      <c r="AF59" s="119"/>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
@@ -9589,12 +9360,7 @@
       <c r="AC60" s="56" t="s">
         <v>607</v>
       </c>
-      <c r="AE60" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF60" s="120">
-        <v>46130</v>
-      </c>
+      <c r="AF60" s="119"/>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
@@ -9680,12 +9446,7 @@
       </c>
       <c r="AB61" s="66"/>
       <c r="AC61" s="56"/>
-      <c r="AE61" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF61" s="120">
-        <v>46135</v>
-      </c>
+      <c r="AF61" s="119"/>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
@@ -9771,12 +9532,7 @@
       </c>
       <c r="AB62" s="66"/>
       <c r="AC62" s="56"/>
-      <c r="AE62" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF62" s="120">
-        <v>46125</v>
-      </c>
+      <c r="AF62" s="119"/>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
@@ -9862,12 +9618,7 @@
       </c>
       <c r="AB63" s="66"/>
       <c r="AC63" s="56"/>
-      <c r="AE63" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF63" s="120">
-        <v>46142</v>
-      </c>
+      <c r="AF63" s="119"/>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
@@ -9953,24 +9704,19 @@
       </c>
       <c r="AB64" s="66"/>
       <c r="AC64" s="56"/>
-      <c r="AE64" s="1">
-        <v>4435</v>
-      </c>
-      <c r="AF64" s="120">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="65" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AF64" s="119"/>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="AA65" s="78"/>
       <c r="AB65" s="78"/>
       <c r="AC65" s="79"/>
     </row>
-    <row r="66" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="AA66" s="80"/>
       <c r="AB66" s="80"/>
       <c r="AC66" s="80"/>
     </row>
-    <row r="67" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q67" s="45"/>
       <c r="R67" s="45"/>
       <c r="S67" s="45"/>
@@ -9985,7 +9731,7 @@
       <c r="AB67" s="80"/>
       <c r="AC67" s="80"/>
     </row>
-    <row r="68" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q68" s="45"/>
       <c r="R68" s="45"/>
       <c r="S68" s="45"/>
@@ -10000,7 +9746,7 @@
       <c r="AB68" s="80"/>
       <c r="AC68" s="80"/>
     </row>
-    <row r="69" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q69" s="45"/>
       <c r="R69" s="45"/>
       <c r="S69" s="45"/>
@@ -10015,7 +9761,7 @@
       <c r="AB69" s="80"/>
       <c r="AC69" s="80"/>
     </row>
-    <row r="70" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q70" s="45"/>
       <c r="R70" s="45"/>
       <c r="S70" s="45"/>
@@ -10030,7 +9776,7 @@
       <c r="AB70" s="80"/>
       <c r="AC70" s="80"/>
     </row>
-    <row r="71" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q71" s="45"/>
       <c r="R71" s="45"/>
       <c r="S71" s="45"/>
@@ -10045,7 +9791,7 @@
       <c r="AB71" s="80"/>
       <c r="AC71" s="80"/>
     </row>
-    <row r="72" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q72" s="45"/>
       <c r="R72" s="45"/>
       <c r="S72" s="45"/>
@@ -10060,7 +9806,7 @@
       <c r="AB72" s="78"/>
       <c r="AC72" s="78"/>
     </row>
-    <row r="73" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q73" s="45"/>
       <c r="R73" s="45"/>
       <c r="S73" s="45"/>
@@ -10075,7 +9821,23 @@
       <c r="AB73" s="80"/>
       <c r="AC73" s="45"/>
     </row>
-    <row r="74" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A74" s="45"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
+      <c r="I74" s="45"/>
+      <c r="J74" s="45"/>
+      <c r="K74" s="45"/>
+      <c r="L74" s="45"/>
+      <c r="M74" s="45"/>
+      <c r="N74" s="45"/>
+      <c r="O74" s="45"/>
+      <c r="P74" s="45"/>
       <c r="Q74" s="45"/>
       <c r="R74" s="45"/>
       <c r="S74" s="45"/>
@@ -10090,7 +9852,23 @@
       <c r="AB74" s="80"/>
       <c r="AC74" s="80"/>
     </row>
-    <row r="75" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A75" s="45"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="45"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="45"/>
+      <c r="L75" s="45"/>
+      <c r="M75" s="45"/>
+      <c r="N75" s="45"/>
+      <c r="O75" s="45"/>
+      <c r="P75" s="45"/>
       <c r="Q75" s="45"/>
       <c r="R75" s="45"/>
       <c r="S75" s="45"/>
@@ -10101,11 +9879,27 @@
       <c r="X75" s="45"/>
       <c r="Y75" s="45"/>
       <c r="Z75" s="45"/>
-      <c r="AA75" s="81"/>
-      <c r="AB75" s="81"/>
-      <c r="AC75" s="81"/>
-    </row>
-    <row r="76" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AA75" s="78"/>
+      <c r="AB75" s="78"/>
+      <c r="AC75" s="78"/>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A76" s="45"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="45"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="45"/>
+      <c r="L76" s="45"/>
+      <c r="M76" s="45"/>
+      <c r="N76" s="45"/>
+      <c r="O76" s="45"/>
+      <c r="P76" s="45"/>
       <c r="Q76" s="45"/>
       <c r="R76" s="45"/>
       <c r="S76" s="45"/>
@@ -10116,11 +9910,27 @@
       <c r="X76" s="45"/>
       <c r="Y76" s="45"/>
       <c r="Z76" s="45"/>
-      <c r="AA76" s="81"/>
-      <c r="AB76" s="44"/>
-      <c r="AC76" s="44"/>
-    </row>
-    <row r="77" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AA76" s="78"/>
+      <c r="AB76" s="80"/>
+      <c r="AC76" s="80"/>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A77" s="45"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="45"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="45"/>
+      <c r="G77" s="45"/>
+      <c r="H77" s="45"/>
+      <c r="I77" s="45"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="45"/>
+      <c r="L77" s="45"/>
+      <c r="M77" s="45"/>
+      <c r="N77" s="45"/>
+      <c r="O77" s="45"/>
+      <c r="P77" s="45"/>
       <c r="Q77" s="45"/>
       <c r="R77" s="45"/>
       <c r="S77" s="45"/>
@@ -10131,11 +9941,27 @@
       <c r="X77" s="45"/>
       <c r="Y77" s="45"/>
       <c r="Z77" s="45"/>
-      <c r="AA77" s="81"/>
-      <c r="AB77" s="44"/>
-      <c r="AC77" s="44"/>
-    </row>
-    <row r="78" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AA77" s="78"/>
+      <c r="AB77" s="80"/>
+      <c r="AC77" s="80"/>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A78" s="45"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
+      <c r="M78" s="45"/>
+      <c r="N78" s="45"/>
+      <c r="O78" s="45"/>
+      <c r="P78" s="45"/>
       <c r="Q78" s="45"/>
       <c r="R78" s="45"/>
       <c r="S78" s="45"/>
@@ -10146,11 +9972,27 @@
       <c r="X78" s="45"/>
       <c r="Y78" s="45"/>
       <c r="Z78" s="45"/>
-      <c r="AA78" s="81"/>
-      <c r="AB78" s="44"/>
-      <c r="AC78" s="44"/>
-    </row>
-    <row r="79" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AA78" s="78"/>
+      <c r="AB78" s="80"/>
+      <c r="AC78" s="80"/>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A79" s="45"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="45"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="45"/>
+      <c r="L79" s="45"/>
+      <c r="M79" s="45"/>
+      <c r="N79" s="45"/>
+      <c r="O79" s="45"/>
+      <c r="P79" s="45"/>
       <c r="Q79" s="45"/>
       <c r="R79" s="45"/>
       <c r="S79" s="45"/>
@@ -10161,13 +10003,27 @@
       <c r="X79" s="45"/>
       <c r="Y79" s="45"/>
       <c r="Z79" s="45"/>
-      <c r="AA79" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB79" s="44"/>
-      <c r="AC79" s="44"/>
-    </row>
-    <row r="80" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AA79" s="78"/>
+      <c r="AB79" s="80"/>
+      <c r="AC79" s="80"/>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A80" s="45"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="45"/>
+      <c r="J80" s="45"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="45"/>
+      <c r="N80" s="45"/>
+      <c r="O80" s="45"/>
+      <c r="P80" s="45"/>
       <c r="Q80" s="45"/>
       <c r="R80" s="45"/>
       <c r="S80" s="45"/>
@@ -10178,19 +10034,27 @@
       <c r="X80" s="45"/>
       <c r="Y80" s="45"/>
       <c r="Z80" s="45"/>
-      <c r="AA80" s="81" t="s">
-        <v>627</v>
-      </c>
-      <c r="AB80" s="44">
-        <f>SUBTOTAL(9,AB76:AB79)</f>
-        <v>0</v>
-      </c>
-      <c r="AC80" s="44">
-        <f>SUBTOTAL(9,AC76:AC79)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="17:29" x14ac:dyDescent="0.35">
+      <c r="AA80" s="78"/>
+      <c r="AB80" s="80"/>
+      <c r="AC80" s="80"/>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A81" s="45"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="45"/>
+      <c r="J81" s="45"/>
+      <c r="K81" s="45"/>
+      <c r="L81" s="45"/>
+      <c r="M81" s="45"/>
+      <c r="N81" s="45"/>
+      <c r="O81" s="45"/>
+      <c r="P81" s="45"/>
       <c r="Q81" s="45"/>
       <c r="R81" s="45"/>
       <c r="S81" s="45"/>
@@ -10205,7 +10069,7 @@
       <c r="AB81" s="45"/>
       <c r="AC81" s="45"/>
     </row>
-    <row r="82" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q82" s="45"/>
       <c r="R82" s="45"/>
       <c r="S82" s="45"/>
@@ -10220,7 +10084,7 @@
       <c r="AB82" s="45"/>
       <c r="AC82" s="45"/>
     </row>
-    <row r="83" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q83" s="45"/>
       <c r="R83" s="45"/>
       <c r="S83" s="45"/>
@@ -10235,7 +10099,7 @@
       <c r="AB83" s="45"/>
       <c r="AC83" s="45"/>
     </row>
-    <row r="84" spans="17:29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="Q84" s="45"/>
       <c r="R84" s="45"/>
       <c r="S84" s="45"/>
@@ -10337,171 +10201,171 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="118" t="s">
+        <v>637</v>
+      </c>
+      <c r="C2" s="118" t="s">
         <v>638</v>
       </c>
-      <c r="C2" s="119" t="s">
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="116" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="117" t="s">
+      <c r="C3" s="117" t="s">
         <v>640</v>
       </c>
-      <c r="C3" s="118" t="s">
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="116" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="117" t="s">
+      <c r="C4" s="117" t="s">
         <v>642</v>
       </c>
-      <c r="C4" s="118" t="s">
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="116" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="117" t="s">
+      <c r="C5" s="117" t="s">
         <v>644</v>
       </c>
-      <c r="C5" s="118" t="s">
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="116" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="117" t="s">
+      <c r="C6" s="117" t="s">
         <v>646</v>
       </c>
-      <c r="C6" s="118" t="s">
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B7" s="116" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="117" t="s">
+      <c r="C7" s="117" t="s">
         <v>648</v>
       </c>
-      <c r="C7" s="118" t="s">
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="116" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B8" s="117" t="s">
+      <c r="C8" s="117" t="s">
         <v>650</v>
       </c>
-      <c r="C8" s="118" t="s">
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B9" s="116" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="117" t="s">
+      <c r="C9" s="117" t="s">
         <v>652</v>
       </c>
-      <c r="C9" s="118" t="s">
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B10" s="116" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="117" t="s">
+      <c r="C10" s="117" t="s">
         <v>654</v>
       </c>
-      <c r="C10" s="118" t="s">
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B11" s="116" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="117" t="s">
+      <c r="C11" s="117" t="s">
         <v>656</v>
       </c>
-      <c r="C11" s="118" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B12" s="116" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="B12" s="117" t="s">
+      <c r="C12" s="117" t="s">
         <v>658</v>
       </c>
-      <c r="C12" s="118" t="s">
+    </row>
+    <row r="13" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="116" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="117" t="s">
+      <c r="C13" s="117" t="s">
         <v>660</v>
       </c>
-      <c r="C13" s="118" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="116" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="117" t="s">
+      <c r="C14" s="117" t="s">
         <v>662</v>
       </c>
-      <c r="C14" s="118" t="s">
+    </row>
+    <row r="15" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="116" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="15" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="117" t="s">
+      <c r="C15" s="117" t="s">
         <v>664</v>
       </c>
-      <c r="C15" s="118" t="s">
+    </row>
+    <row r="16" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="116" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="117" t="s">
+      <c r="C16" s="117" t="s">
         <v>666</v>
       </c>
-      <c r="C16" s="118" t="s">
+    </row>
+    <row r="17" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="116" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117" t="s">
+      <c r="C17" s="117" t="s">
         <v>668</v>
       </c>
-      <c r="C17" s="118" t="s">
+    </row>
+    <row r="18" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="116" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="117" t="s">
+      <c r="C18" s="117" t="s">
         <v>670</v>
       </c>
-      <c r="C18" s="118" t="s">
+    </row>
+    <row r="19" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="116" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="117" t="s">
+      <c r="C19" s="117" t="s">
         <v>672</v>
       </c>
-      <c r="C19" s="118" t="s">
+    </row>
+    <row r="20" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="116" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="117" t="s">
+      <c r="C20" s="117" t="s">
         <v>674</v>
       </c>
-      <c r="C20" s="118" t="s">
+    </row>
+    <row r="21" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="116" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="21" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="117" t="s">
+      <c r="C21" s="117" t="s">
         <v>676</v>
       </c>
-      <c r="C21" s="118" t="s">
+    </row>
+    <row r="22" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="116" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="22" spans="2:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="117" t="s">
+      <c r="C22" s="117" t="s">
         <v>678</v>
-      </c>
-      <c r="C22" s="118" t="s">
-        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -10520,232 +10384,232 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="113" t="s">
+        <v>679</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>637</v>
+      </c>
+      <c r="D4" s="113" t="s">
         <v>680</v>
       </c>
-      <c r="C4" s="114" t="s">
-        <v>638</v>
-      </c>
-      <c r="D4" s="114" t="s">
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="114">
+        <v>1</v>
+      </c>
+      <c r="C5" s="115" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="115">
-        <v>1</v>
-      </c>
-      <c r="C5" s="116" t="s">
+      <c r="D5" s="125" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="114">
+        <v>2</v>
+      </c>
+      <c r="C6" s="115" t="s">
         <v>682</v>
       </c>
-      <c r="D5" s="126" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="115">
-        <v>2</v>
-      </c>
-      <c r="C6" s="116" t="s">
+      <c r="D6" s="125"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="114">
+        <v>3</v>
+      </c>
+      <c r="C7" s="115" t="s">
         <v>683</v>
       </c>
-      <c r="D6" s="126"/>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="115">
-        <v>3</v>
-      </c>
-      <c r="C7" s="116" t="s">
+      <c r="D7" s="114" t="s">
         <v>684</v>
       </c>
-      <c r="D7" s="115" t="s">
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B8" s="114">
+        <v>4</v>
+      </c>
+      <c r="C8" s="115" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="115">
-        <v>4</v>
-      </c>
-      <c r="C8" s="116" t="s">
+      <c r="D8" s="114" t="s">
         <v>686</v>
       </c>
-      <c r="D8" s="115" t="s">
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="114">
+        <v>5</v>
+      </c>
+      <c r="C9" s="115" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="115">
-        <v>5</v>
-      </c>
-      <c r="C9" s="116" t="s">
+      <c r="D9" s="114" t="s">
         <v>688</v>
       </c>
-      <c r="D9" s="115" t="s">
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="114">
+        <v>6</v>
+      </c>
+      <c r="C10" s="115" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="115">
-        <v>6</v>
-      </c>
-      <c r="C10" s="116" t="s">
+      <c r="D10" s="114" t="s">
         <v>690</v>
       </c>
-      <c r="D10" s="115" t="s">
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="114">
+        <v>7</v>
+      </c>
+      <c r="C11" s="115" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="115">
-        <v>7</v>
-      </c>
-      <c r="C11" s="116" t="s">
+      <c r="D11" s="114" t="s">
         <v>692</v>
       </c>
-      <c r="D11" s="115" t="s">
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="114">
+        <v>8</v>
+      </c>
+      <c r="C12" s="115" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="115">
-        <v>8</v>
-      </c>
-      <c r="C12" s="116" t="s">
+      <c r="D12" s="114" t="s">
         <v>694</v>
       </c>
-      <c r="D12" s="115" t="s">
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="114">
+        <v>9</v>
+      </c>
+      <c r="C13" s="115" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="115">
-        <v>9</v>
-      </c>
-      <c r="C13" s="116" t="s">
+      <c r="D13" s="114" t="s">
         <v>696</v>
       </c>
-      <c r="D13" s="115" t="s">
+    </row>
+    <row r="14" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B14" s="114">
+        <v>10</v>
+      </c>
+      <c r="C14" s="115" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B14" s="115">
-        <v>10</v>
-      </c>
-      <c r="C14" s="116" t="s">
+      <c r="D14" s="114" t="s">
         <v>698</v>
       </c>
-      <c r="D14" s="115" t="s">
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B15" s="114">
+        <v>11</v>
+      </c>
+      <c r="C15" s="115" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="115">
-        <v>11</v>
-      </c>
-      <c r="C15" s="116" t="s">
+      <c r="D15" s="114" t="s">
         <v>700</v>
       </c>
-      <c r="D15" s="115" t="s">
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B16" s="114">
+        <v>12</v>
+      </c>
+      <c r="C16" s="115" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="115">
-        <v>12</v>
-      </c>
-      <c r="C16" s="116" t="s">
+      <c r="D16" s="114" t="s">
         <v>702</v>
       </c>
-      <c r="D16" s="115" t="s">
+    </row>
+    <row r="17" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B17" s="114">
+        <v>13</v>
+      </c>
+      <c r="C17" s="115" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B17" s="115">
-        <v>13</v>
-      </c>
-      <c r="C17" s="116" t="s">
+      <c r="D17" s="114" t="s">
         <v>704</v>
       </c>
-      <c r="D17" s="115" t="s">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="114">
+        <v>14</v>
+      </c>
+      <c r="C18" s="115" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="115">
-        <v>14</v>
-      </c>
-      <c r="C18" s="116" t="s">
+      <c r="D18" s="114" t="s">
         <v>706</v>
       </c>
-      <c r="D18" s="115" t="s">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="114">
+        <v>15</v>
+      </c>
+      <c r="C19" s="115" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="115">
-        <v>15</v>
-      </c>
-      <c r="C19" s="116" t="s">
+      <c r="D19" s="114" t="s">
         <v>708</v>
       </c>
-      <c r="D19" s="115" t="s">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="114">
+        <v>16</v>
+      </c>
+      <c r="C20" s="115" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="115">
-        <v>16</v>
-      </c>
-      <c r="C20" s="116" t="s">
+      <c r="D20" s="114" t="s">
         <v>710</v>
       </c>
-      <c r="D20" s="115" t="s">
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="114">
+        <v>17</v>
+      </c>
+      <c r="C21" s="115" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="115">
-        <v>17</v>
-      </c>
-      <c r="C21" s="116" t="s">
+      <c r="D21" s="114" t="s">
         <v>712</v>
       </c>
-      <c r="D21" s="115" t="s">
+    </row>
+    <row r="22" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="114">
+        <v>18</v>
+      </c>
+      <c r="C22" s="115" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B22" s="115">
-        <v>18</v>
-      </c>
-      <c r="C22" s="116" t="s">
+      <c r="D22" s="115" t="s">
         <v>714</v>
       </c>
-      <c r="D22" s="116" t="s">
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="114">
+        <v>19</v>
+      </c>
+      <c r="C23" s="115" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="115">
-        <v>19</v>
-      </c>
-      <c r="C23" s="116" t="s">
+      <c r="D23" s="115" t="s">
         <v>716</v>
       </c>
-      <c r="D23" s="116" t="s">
+    </row>
+    <row r="24" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B24" s="114">
+        <v>20</v>
+      </c>
+      <c r="C24" s="115" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B24" s="115">
-        <v>20</v>
-      </c>
-      <c r="C24" s="116" t="s">
+      <c r="D24" s="115" t="s">
         <v>718</v>
-      </c>
-      <c r="D24" s="116" t="s">
-        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -10786,8 +10650,8 @@
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z64,11,0)</f>
         <v>ANMOL KUMAR</v>
       </c>
-      <c r="E2" s="82" t="s">
-        <v>629</v>
+      <c r="E2" s="81" t="s">
+        <v>628</v>
       </c>
       <c r="F2" s="52" t="str">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC88,27,0)</f>
@@ -10802,7 +10666,7 @@
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z64,3,0)</f>
         <v>39056</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="81" t="s">
         <v>601</v>
       </c>
       <c r="F3" s="52">
@@ -10818,8 +10682,8 @@
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z64,13,0)</f>
         <v>SHIV POOJAN</v>
       </c>
-      <c r="E4" s="82" t="s">
-        <v>628</v>
+      <c r="E4" s="81" t="s">
+        <v>627</v>
       </c>
       <c r="F4" s="52">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A2:AC90,29,0)</f>
@@ -10844,20 +10708,20 @@
         <v>40544</v>
       </c>
       <c r="F6" s="44" t="s">
+        <v>629</v>
+      </c>
+      <c r="G6" s="44" t="s">
         <v>630</v>
       </c>
-      <c r="G6" s="44" t="s">
-        <v>631</v>
-      </c>
       <c r="H6" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I6" s="44"/>
     </row>
     <row r="7" spans="2:16" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B7" s="49"/>
       <c r="C7" s="48"/>
-      <c r="E7" s="84"/>
+      <c r="E7" s="83"/>
       <c r="F7" s="44" t="s">
         <v>62</v>
       </c>
@@ -10898,7 +10762,7 @@
       <c r="B9" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="82">
         <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z72,25,0)</f>
         <v>9519725292</v>
       </c>
@@ -10915,13 +10779,13 @@
         <v>awanitk94@gmail.com</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I10" s="44"/>
       <c r="P10">
@@ -10993,13 +10857,13 @@
         <v>OBC</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I15" s="44"/>
     </row>
@@ -11085,334 +10949,334 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="128" t="s">
-        <v>635</v>
-      </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
+      <c r="A1" s="127" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="127" t="s">
-        <v>727</v>
-      </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
+      <c r="A2" s="126" t="s">
+        <v>726</v>
+      </c>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="121" t="s">
+        <v>720</v>
+      </c>
+      <c r="B3" s="121" t="s">
         <v>721</v>
       </c>
-      <c r="B3" s="122" t="s">
+      <c r="C3" s="121" t="s">
         <v>722</v>
       </c>
-      <c r="C3" s="122" t="s">
+      <c r="D3" s="121" t="s">
         <v>723</v>
       </c>
-      <c r="D3" s="122" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="122">
+        <v>1</v>
+      </c>
+      <c r="B4" s="123">
+        <v>37239</v>
+      </c>
+      <c r="C4" s="122" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="122" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="123">
-        <v>1</v>
-      </c>
-      <c r="B4" s="124">
-        <v>37239</v>
-      </c>
-      <c r="C4" s="123" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="123" t="s">
+    <row r="5" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="122">
+        <v>2</v>
+      </c>
+      <c r="B5" s="123">
+        <v>39076</v>
+      </c>
+      <c r="C5" s="122" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="122">
+        <v>3</v>
+      </c>
+      <c r="B6" s="123">
+        <v>37253</v>
+      </c>
+      <c r="C6" s="122" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="122">
+        <v>4</v>
+      </c>
+      <c r="B7" s="123">
+        <v>39007</v>
+      </c>
+      <c r="C7" s="122" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="122">
+        <v>5</v>
+      </c>
+      <c r="B8" s="123">
+        <v>37181</v>
+      </c>
+      <c r="C8" s="122" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="122">
+        <v>6</v>
+      </c>
+      <c r="B9" s="123">
+        <v>38995</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>574</v>
+      </c>
+      <c r="D9" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="122">
+        <v>7</v>
+      </c>
+      <c r="B10" s="123">
+        <v>37070</v>
+      </c>
+      <c r="C10" s="122" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="122">
+        <v>8</v>
+      </c>
+      <c r="B11" s="123">
+        <v>38990</v>
+      </c>
+      <c r="C11" s="122" t="s">
+        <v>391</v>
+      </c>
+      <c r="D11" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="122">
+        <v>9</v>
+      </c>
+      <c r="B12" s="123">
+        <v>38999</v>
+      </c>
+      <c r="C12" s="122" t="s">
+        <v>462</v>
+      </c>
+      <c r="D12" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="122">
+        <v>10</v>
+      </c>
+      <c r="B13" s="123">
+        <v>37069</v>
+      </c>
+      <c r="C13" s="122" t="s">
+        <v>599</v>
+      </c>
+      <c r="D13" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="122">
+        <v>11</v>
+      </c>
+      <c r="B14" s="123">
+        <v>37068</v>
+      </c>
+      <c r="C14" s="122" t="s">
+        <v>481</v>
+      </c>
+      <c r="D14" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="122">
+        <v>12</v>
+      </c>
+      <c r="B15" s="123">
+        <v>37143</v>
+      </c>
+      <c r="C15" s="122" t="s">
+        <v>506</v>
+      </c>
+      <c r="D15" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="122">
+        <v>13</v>
+      </c>
+      <c r="B16" s="123">
+        <v>37124</v>
+      </c>
+      <c r="C16" s="122" t="s">
+        <v>542</v>
+      </c>
+      <c r="D16" s="122" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="122">
+        <v>14</v>
+      </c>
+      <c r="B17" s="123">
+        <v>39032</v>
+      </c>
+      <c r="C17" s="122" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="123">
-        <v>2</v>
-      </c>
-      <c r="B5" s="124">
-        <v>39076</v>
-      </c>
-      <c r="C5" s="123" t="s">
-        <v>351</v>
-      </c>
-      <c r="D5" s="123" t="s">
+    <row r="18" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="122">
+        <v>15</v>
+      </c>
+      <c r="B18" s="123">
+        <v>37170</v>
+      </c>
+      <c r="C18" s="122" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="123">
-        <v>3</v>
-      </c>
-      <c r="B6" s="124">
-        <v>37253</v>
-      </c>
-      <c r="C6" s="123" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" s="123" t="s">
+    <row r="19" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="122">
+        <v>16</v>
+      </c>
+      <c r="B19" s="123">
+        <v>39033</v>
+      </c>
+      <c r="C19" s="122" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="123">
-        <v>4</v>
-      </c>
-      <c r="B7" s="124">
-        <v>39007</v>
-      </c>
-      <c r="C7" s="123" t="s">
-        <v>239</v>
-      </c>
-      <c r="D7" s="123" t="s">
+    <row r="20" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="122">
+        <v>17</v>
+      </c>
+      <c r="B20" s="123">
+        <v>37242</v>
+      </c>
+      <c r="C20" s="122" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="123">
-        <v>5</v>
-      </c>
-      <c r="B8" s="124">
-        <v>37181</v>
-      </c>
-      <c r="C8" s="123" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" s="123" t="s">
+    <row r="21" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="122">
+        <v>18</v>
+      </c>
+      <c r="B21" s="123">
+        <v>37111</v>
+      </c>
+      <c r="C21" s="122" t="s">
+        <v>598</v>
+      </c>
+      <c r="D21" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="123">
-        <v>6</v>
-      </c>
-      <c r="B9" s="124">
-        <v>38995</v>
-      </c>
-      <c r="C9" s="123" t="s">
-        <v>574</v>
-      </c>
-      <c r="D9" s="123" t="s">
+    <row r="22" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="122">
+        <v>19</v>
+      </c>
+      <c r="B22" s="123">
+        <v>38962</v>
+      </c>
+      <c r="C22" s="122" t="s">
+        <v>407</v>
+      </c>
+      <c r="D22" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="123">
-        <v>7</v>
-      </c>
-      <c r="B10" s="124">
-        <v>37070</v>
-      </c>
-      <c r="C10" s="123" t="s">
-        <v>382</v>
-      </c>
-      <c r="D10" s="123" t="s">
+    <row r="23" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="122">
+        <v>20</v>
+      </c>
+      <c r="B23" s="123">
+        <v>37110</v>
+      </c>
+      <c r="C23" s="122" t="s">
+        <v>432</v>
+      </c>
+      <c r="D23" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="123">
-        <v>8</v>
-      </c>
-      <c r="B11" s="124">
-        <v>38990</v>
-      </c>
-      <c r="C11" s="123" t="s">
-        <v>391</v>
-      </c>
-      <c r="D11" s="123" t="s">
+    <row r="24" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="122">
+        <v>21</v>
+      </c>
+      <c r="B24" s="123">
+        <v>37113</v>
+      </c>
+      <c r="C24" s="122" t="s">
+        <v>521</v>
+      </c>
+      <c r="D24" s="122" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="123">
-        <v>9</v>
-      </c>
-      <c r="B12" s="124">
-        <v>38999</v>
-      </c>
-      <c r="C12" s="123" t="s">
-        <v>462</v>
-      </c>
-      <c r="D12" s="123" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="123">
-        <v>10</v>
-      </c>
-      <c r="B13" s="124">
-        <v>37069</v>
-      </c>
-      <c r="C13" s="123" t="s">
-        <v>599</v>
-      </c>
-      <c r="D13" s="123" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="123">
-        <v>11</v>
-      </c>
-      <c r="B14" s="124">
-        <v>37068</v>
-      </c>
-      <c r="C14" s="123" t="s">
-        <v>481</v>
-      </c>
-      <c r="D14" s="123" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="123">
-        <v>12</v>
-      </c>
-      <c r="B15" s="124">
-        <v>37143</v>
-      </c>
-      <c r="C15" s="123" t="s">
-        <v>506</v>
-      </c>
-      <c r="D15" s="123" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="123">
-        <v>13</v>
-      </c>
-      <c r="B16" s="124">
-        <v>37124</v>
-      </c>
-      <c r="C16" s="123" t="s">
-        <v>542</v>
-      </c>
-      <c r="D16" s="123" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="123">
-        <v>14</v>
-      </c>
-      <c r="B17" s="124">
-        <v>39032</v>
-      </c>
-      <c r="C17" s="123" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="123">
-        <v>15</v>
-      </c>
-      <c r="B18" s="124">
-        <v>37170</v>
-      </c>
-      <c r="C18" s="123" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="123">
-        <v>16</v>
-      </c>
-      <c r="B19" s="124">
-        <v>39033</v>
-      </c>
-      <c r="C19" s="123" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="123">
-        <v>17</v>
-      </c>
-      <c r="B20" s="124">
-        <v>37242</v>
-      </c>
-      <c r="C20" s="123" t="s">
-        <v>256</v>
-      </c>
-      <c r="D20" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="123">
-        <v>18</v>
-      </c>
-      <c r="B21" s="124">
-        <v>37111</v>
-      </c>
-      <c r="C21" s="123" t="s">
-        <v>598</v>
-      </c>
-      <c r="D21" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="123">
-        <v>19</v>
-      </c>
-      <c r="B22" s="124">
-        <v>38962</v>
-      </c>
-      <c r="C22" s="123" t="s">
-        <v>407</v>
-      </c>
-      <c r="D22" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="123">
-        <v>20</v>
-      </c>
-      <c r="B23" s="124">
-        <v>37110</v>
-      </c>
-      <c r="C23" s="123" t="s">
-        <v>432</v>
-      </c>
-      <c r="D23" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="123">
-        <v>21</v>
-      </c>
-      <c r="B24" s="124">
-        <v>37113</v>
-      </c>
-      <c r="C24" s="123" t="s">
-        <v>521</v>
-      </c>
-      <c r="D24" s="123" t="s">
-        <v>726</v>
-      </c>
-    </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="121"/>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
+      <c r="A25" s="120"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="120"/>
     </row>
   </sheetData>
   <sortState ref="A2:D23">
